--- a/Result/profitability/3290.xlsx
+++ b/Result/profitability/3290.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.765</v>
+        <v>0.8650000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>29.99875</v>
+        <v>28.51</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>0.71125</v>
+        <v>0.8275</v>
       </c>
       <c r="N3" t="n">
-        <v>28.42375</v>
+        <v>27.7225</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7625</v>
+        <v>0.89375</v>
       </c>
       <c r="N4" t="n">
-        <v>28.295</v>
+        <v>27.815</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7212499999999999</v>
+        <v>0.88375</v>
       </c>
       <c r="N5" t="n">
-        <v>27.7875</v>
+        <v>27.11625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.76375</v>
       </c>
       <c r="N6" t="n">
-        <v>26.9575</v>
+        <v>26.10375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.59875</v>
+        <v>0.6787500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>26.04875</v>
+        <v>25.34125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.51375</v>
+        <v>0.35375</v>
       </c>
       <c r="N8" t="n">
-        <v>25.3</v>
+        <v>25.875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>955</v>
+      </c>
+      <c r="D75" t="n">
+        <v>719</v>
+      </c>
+      <c r="E75" t="n">
+        <v>236</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="G75" t="n">
+        <v>25</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>99</v>
+      </c>
+      <c r="J75" t="n">
+        <v>124</v>
+      </c>
+      <c r="K75" t="n">
+        <v>124</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.89625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.0675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4830188679245282</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.599999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2284011916583912</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.370000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1783460644304218</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
